--- a/public/observations-summary.xlsx
+++ b/public/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="180">
   <si>
     <t>Profile</t>
   </si>
@@ -89,7 +89,7 @@
     <t>PGHD AlcholUse Profile</t>
   </si>
   <si>
-    <t>null#74013-4</t>
+    <t>null#numberOfAlcoholicBeverages, null#74013-4</t>
   </si>
   <si>
     <t>pghd-audiogram</t>
@@ -101,7 +101,7 @@
     <t>Observation Category Codes#exam</t>
   </si>
   <si>
-    <t>null#89015-2</t>
+    <t>null#Audiogram, null#89015-2</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1 (example)</t>
@@ -209,10 +209,13 @@
     <t>PGHD Electrocardiogram Profile</t>
   </si>
   <si>
-    <t>ECG Classification Codes#classification</t>
-  </si>
-  <si>
-    <t>ECG Classification Codes#symptomsStatus</t>
+    <t>null#electrocardiogram</t>
+  </si>
+  <si>
+    <t>ECG Codes#classification</t>
+  </si>
+  <si>
+    <t>ECG Codes#symptomsStatus</t>
   </si>
   <si>
     <t>pghd-food</t>
@@ -221,6 +224,9 @@
     <t>PGHD Food Profile</t>
   </si>
   <si>
+    <t>null#food</t>
+  </si>
+  <si>
     <t>stringĵ</t>
   </si>
   <si>
@@ -239,6 +245,9 @@
     <t>PGHD HearingSensitivity Profile</t>
   </si>
   <si>
+    <t>null#hearingSensitivity</t>
+  </si>
+  <si>
     <t>Hearing Sensitivity Codes#frequency</t>
   </si>
   <si>
@@ -254,6 +263,9 @@
     <t>PGHD Heartbeat Profile</t>
   </si>
   <si>
+    <t>null#heartBeatSeries</t>
+  </si>
+  <si>
     <t>Quantity</t>
   </si>
   <si>
@@ -338,6 +350,9 @@
     <t>PGHD State of Mind Profile</t>
   </si>
   <si>
+    <t>null#stateOfMind</t>
+  </si>
+  <si>
     <t>State of Mind Codes#kind</t>
   </si>
   <si>
@@ -368,7 +383,7 @@
     <t>PGHD Pregnancy Status Profile</t>
   </si>
   <si>
-    <t>null#82810-3</t>
+    <t>null#pregnancy, null#82810-3</t>
   </si>
   <si>
     <t>pghd-reproductive-health</t>
@@ -1247,7 +1262,7 @@
         <v>14</v>
       </c>
       <c r="E17" t="s" s="2">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="F17" t="s" s="2">
         <v>30</v>
@@ -1300,7 +1315,7 @@
         <v>14</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19">
@@ -1335,15 +1350,15 @@
         <v>14</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C20" t="s" s="2">
         <v>21</v>
@@ -1352,7 +1367,7 @@
         <v>14</v>
       </c>
       <c r="E20" t="s" s="2">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="F20" t="s" s="2">
         <v>30</v>
@@ -1361,7 +1376,7 @@
         <v>16</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>18</v>
@@ -1375,10 +1390,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C21" t="s" s="2">
         <v>21</v>
@@ -1390,7 +1405,7 @@
         <v>14</v>
       </c>
       <c r="F21" t="s" s="2">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>16</v>
@@ -1410,10 +1425,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C22" t="s" s="2">
         <v>28</v>
@@ -1422,7 +1437,7 @@
         <v>14</v>
       </c>
       <c r="E22" t="s" s="2">
-        <v>14</v>
+        <v>77</v>
       </c>
       <c r="F22" t="s" s="2">
         <v>30</v>
@@ -1448,7 +1463,7 @@
         <v>14</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C23" t="s" s="2">
         <v>14</v>
@@ -1475,7 +1490,7 @@
         <v>14</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24">
@@ -1483,7 +1498,7 @@
         <v>14</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C24" t="s" s="2">
         <v>14</v>
@@ -1510,7 +1525,7 @@
         <v>14</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25">
@@ -1518,7 +1533,7 @@
         <v>14</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C25" t="s" s="2">
         <v>14</v>
@@ -1545,15 +1560,15 @@
         <v>14</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C26" t="s" s="2">
         <v>28</v>
@@ -1562,7 +1577,7 @@
         <v>14</v>
       </c>
       <c r="E26" t="s" s="2">
-        <v>14</v>
+        <v>83</v>
       </c>
       <c r="F26" t="s" s="2">
         <v>30</v>
@@ -1588,7 +1603,7 @@
         <v>14</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C27" t="s" s="2">
         <v>14</v>
@@ -1606,7 +1621,7 @@
         <v>14</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>18</v>
@@ -1615,15 +1630,15 @@
         <v>14</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C28" t="s" s="2">
         <v>34</v>
@@ -1632,7 +1647,7 @@
         <v>14</v>
       </c>
       <c r="E28" t="s" s="2">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F28" t="s" s="2">
         <v>39</v>
@@ -1655,10 +1670,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C29" t="s" s="2">
         <v>21</v>
@@ -1667,13 +1682,13 @@
         <v>14</v>
       </c>
       <c r="E29" t="s" s="2">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="F29" t="s" s="2">
         <v>30</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>17</v>
@@ -1690,10 +1705,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C30" t="s" s="2">
         <v>13</v>
@@ -1705,7 +1720,7 @@
         <v>14</v>
       </c>
       <c r="F30" t="s" s="2">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>16</v>
@@ -1725,10 +1740,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C31" t="s" s="2">
         <v>13</v>
@@ -1740,13 +1755,13 @@
         <v>14</v>
       </c>
       <c r="F31" t="s" s="2">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>16</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>18</v>
@@ -1760,10 +1775,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C32" t="s" s="2">
         <v>21</v>
@@ -1775,7 +1790,7 @@
         <v>14</v>
       </c>
       <c r="F32" t="s" s="2">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>16</v>
@@ -1795,13 +1810,13 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D33" t="s" s="2">
         <v>14</v>
@@ -1810,7 +1825,7 @@
         <v>14</v>
       </c>
       <c r="F33" t="s" s="2">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>16</v>
@@ -1833,7 +1848,7 @@
         <v>14</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C34" t="s" s="2">
         <v>14</v>
@@ -1851,7 +1866,7 @@
         <v>14</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>18</v>
@@ -1868,7 +1883,7 @@
         <v>14</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C35" t="s" s="2">
         <v>14</v>
@@ -1886,7 +1901,7 @@
         <v>14</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>18</v>
@@ -1895,7 +1910,7 @@
         <v>14</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="36">
@@ -1903,7 +1918,7 @@
         <v>14</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C36" t="s" s="2">
         <v>14</v>
@@ -1921,7 +1936,7 @@
         <v>14</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>18</v>
@@ -1930,27 +1945,27 @@
         <v>14</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D37" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>14</v>
+        <v>112</v>
       </c>
       <c r="F37" t="s" s="2">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>16</v>
@@ -1973,26 +1988,26 @@
         <v>14</v>
       </c>
       <c r="B38" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="C38" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D38" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E38" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F38" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H38" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="C38" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="D38" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E38" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="F38" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="G38" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="H38" t="s" s="2">
-        <v>103</v>
-      </c>
       <c r="I38" t="s" s="2">
         <v>18</v>
       </c>
@@ -2000,7 +2015,7 @@
         <v>14</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="39">
@@ -2008,7 +2023,7 @@
         <v>14</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C39" t="s" s="2">
         <v>14</v>
@@ -2026,7 +2041,7 @@
         <v>14</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>18</v>
@@ -2035,7 +2050,7 @@
         <v>14</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="40">
@@ -2043,26 +2058,26 @@
         <v>14</v>
       </c>
       <c r="B40" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="C40" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D40" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E40" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F40" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H40" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="C40" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="D40" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E40" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="F40" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="G40" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="H40" t="s" s="2">
-        <v>103</v>
-      </c>
       <c r="I40" t="s" s="2">
         <v>18</v>
       </c>
@@ -2070,7 +2085,7 @@
         <v>14</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="41">
@@ -2078,26 +2093,26 @@
         <v>14</v>
       </c>
       <c r="B41" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="C41" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D41" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E41" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F41" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H41" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="C41" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="D41" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E41" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="F41" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="G41" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="H41" t="s" s="2">
-        <v>103</v>
-      </c>
       <c r="I41" t="s" s="2">
         <v>18</v>
       </c>
@@ -2105,7 +2120,7 @@
         <v>14</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="42">
@@ -2113,26 +2128,26 @@
         <v>14</v>
       </c>
       <c r="B42" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="C42" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D42" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E42" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F42" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H42" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="C42" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="D42" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E42" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="F42" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="G42" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="H42" t="s" s="2">
-        <v>103</v>
-      </c>
       <c r="I42" t="s" s="2">
         <v>18</v>
       </c>
@@ -2140,15 +2155,15 @@
         <v>14</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>112</v>
+        <v>117</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="C43" t="s" s="2">
         <v>34</v>
@@ -2157,7 +2172,7 @@
         <v>14</v>
       </c>
       <c r="E43" t="s" s="2">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F43" t="s" s="2">
         <v>39</v>
@@ -2180,10 +2195,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C44" t="s" s="2">
         <v>21</v>
@@ -2192,7 +2207,7 @@
         <v>14</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F44" t="s" s="2">
         <v>30</v>
@@ -2201,7 +2216,7 @@
         <v>16</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>18</v>
@@ -2215,10 +2230,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C45" t="s" s="2">
         <v>21</v>
@@ -2230,13 +2245,13 @@
         <v>14</v>
       </c>
       <c r="F45" t="s" s="2">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>16</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>18</v>
@@ -2250,10 +2265,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="C46" t="s" s="2">
         <v>34</v>
@@ -2262,7 +2277,7 @@
         <v>14</v>
       </c>
       <c r="E46" t="s" s="2">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="F46" t="s" s="2">
         <v>39</v>
@@ -2285,10 +2300,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="C47" t="s" s="2">
         <v>21</v>
@@ -2300,7 +2315,7 @@
         <v>14</v>
       </c>
       <c r="F47" t="s" s="2">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>16</v>
@@ -2320,10 +2335,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C48" t="s" s="2">
         <v>21</v>
@@ -2335,13 +2350,13 @@
         <v>14</v>
       </c>
       <c r="F48" t="s" s="2">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>16</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>18</v>
@@ -2355,10 +2370,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C49" t="s" s="2">
         <v>21</v>
@@ -2367,13 +2382,13 @@
         <v>14</v>
       </c>
       <c r="E49" t="s" s="2">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="F49" t="s" s="2">
         <v>30</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>31</v>
@@ -2393,7 +2408,7 @@
         <v>14</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C50" t="s" s="2">
         <v>14</v>
@@ -2411,7 +2426,7 @@
         <v>14</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>18</v>
@@ -2420,7 +2435,7 @@
         <v>14</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>134</v>
+        <v>139</v>
       </c>
     </row>
     <row r="51">
@@ -2428,7 +2443,7 @@
         <v>14</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C51" t="s" s="2">
         <v>14</v>
@@ -2446,7 +2461,7 @@
         <v>14</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>18</v>
@@ -2455,7 +2470,7 @@
         <v>14</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="52">
@@ -2463,7 +2478,7 @@
         <v>14</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C52" t="s" s="2">
         <v>14</v>
@@ -2481,7 +2496,7 @@
         <v>14</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>18</v>
@@ -2490,7 +2505,7 @@
         <v>14</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="53">
@@ -2498,7 +2513,7 @@
         <v>14</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C53" t="s" s="2">
         <v>14</v>
@@ -2516,7 +2531,7 @@
         <v>14</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>18</v>
@@ -2525,7 +2540,7 @@
         <v>14</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>137</v>
+        <v>142</v>
       </c>
     </row>
     <row r="54">
@@ -2533,7 +2548,7 @@
         <v>14</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C54" t="s" s="2">
         <v>14</v>
@@ -2551,7 +2566,7 @@
         <v>14</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>18</v>
@@ -2560,7 +2575,7 @@
         <v>14</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
     </row>
     <row r="55">
@@ -2568,7 +2583,7 @@
         <v>14</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C55" t="s" s="2">
         <v>14</v>
@@ -2586,7 +2601,7 @@
         <v>14</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>18</v>
@@ -2595,7 +2610,7 @@
         <v>14</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>139</v>
+        <v>144</v>
       </c>
     </row>
     <row r="56">
@@ -2603,7 +2618,7 @@
         <v>14</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C56" t="s" s="2">
         <v>14</v>
@@ -2621,7 +2636,7 @@
         <v>14</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>18</v>
@@ -2630,7 +2645,7 @@
         <v>14</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>140</v>
+        <v>145</v>
       </c>
     </row>
     <row r="57">
@@ -2638,7 +2653,7 @@
         <v>14</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C57" t="s" s="2">
         <v>14</v>
@@ -2656,7 +2671,7 @@
         <v>14</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>18</v>
@@ -2665,7 +2680,7 @@
         <v>14</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>141</v>
+        <v>146</v>
       </c>
     </row>
     <row r="58">
@@ -2673,7 +2688,7 @@
         <v>14</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C58" t="s" s="2">
         <v>14</v>
@@ -2691,7 +2706,7 @@
         <v>14</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>18</v>
@@ -2700,7 +2715,7 @@
         <v>14</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="59">
@@ -2708,7 +2723,7 @@
         <v>14</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C59" t="s" s="2">
         <v>14</v>
@@ -2726,7 +2741,7 @@
         <v>14</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>18</v>
@@ -2735,7 +2750,7 @@
         <v>14</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>143</v>
+        <v>148</v>
       </c>
     </row>
     <row r="60">
@@ -2743,7 +2758,7 @@
         <v>14</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C60" t="s" s="2">
         <v>14</v>
@@ -2761,7 +2776,7 @@
         <v>14</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>18</v>
@@ -2770,7 +2785,7 @@
         <v>14</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>144</v>
+        <v>149</v>
       </c>
     </row>
     <row r="61">
@@ -2778,7 +2793,7 @@
         <v>14</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C61" t="s" s="2">
         <v>14</v>
@@ -2796,7 +2811,7 @@
         <v>14</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>18</v>
@@ -2805,7 +2820,7 @@
         <v>14</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="62">
@@ -2813,7 +2828,7 @@
         <v>14</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C62" t="s" s="2">
         <v>14</v>
@@ -2831,7 +2846,7 @@
         <v>14</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>18</v>
@@ -2840,15 +2855,15 @@
         <v>14</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>147</v>
+        <v>152</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="C63" t="s" s="2">
         <v>21</v>
@@ -2857,16 +2872,16 @@
         <v>14</v>
       </c>
       <c r="E63" t="s" s="2">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="F63" t="s" s="2">
         <v>30</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>18</v>
@@ -2883,7 +2898,7 @@
         <v>14</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="C64" t="s" s="2">
         <v>14</v>
@@ -2901,7 +2916,7 @@
         <v>14</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>18</v>
@@ -2910,7 +2925,7 @@
         <v>14</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>152</v>
+        <v>157</v>
       </c>
     </row>
     <row r="65">
@@ -2918,7 +2933,7 @@
         <v>14</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="C65" t="s" s="2">
         <v>14</v>
@@ -2936,7 +2951,7 @@
         <v>14</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>18</v>
@@ -2945,15 +2960,15 @@
         <v>14</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>153</v>
+        <v>158</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="C66" t="s" s="2">
         <v>21</v>
@@ -2962,16 +2977,16 @@
         <v>14</v>
       </c>
       <c r="E66" t="s" s="2">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="F66" t="s" s="2">
         <v>30</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>18</v>
@@ -2985,10 +3000,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C67" t="s" s="2">
         <v>21</v>
@@ -3000,13 +3015,13 @@
         <v>14</v>
       </c>
       <c r="F67" t="s" s="2">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>16</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>18</v>
@@ -3020,10 +3035,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C68" t="s" s="2">
         <v>28</v>
@@ -3035,13 +3050,13 @@
         <v>14</v>
       </c>
       <c r="F68" t="s" s="2">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>16</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>18</v>
@@ -3055,10 +3070,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="C69" t="s" s="2">
         <v>21</v>
@@ -3070,13 +3085,13 @@
         <v>14</v>
       </c>
       <c r="F69" t="s" s="2">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="G69" t="s" s="2">
         <v>16</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>18</v>
@@ -3090,10 +3105,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="C70" t="s" s="2">
         <v>34</v>
@@ -3125,10 +3140,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="C71" t="s" s="2">
         <v>28</v>
@@ -3140,13 +3155,13 @@
         <v>14</v>
       </c>
       <c r="F71" t="s" s="2">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="G71" t="s" s="2">
         <v>16</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>18</v>
@@ -3160,10 +3175,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="C72" t="s" s="2">
         <v>13</v>
@@ -3175,7 +3190,7 @@
         <v>14</v>
       </c>
       <c r="F72" t="s" s="2">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="G72" t="s" s="2">
         <v>16</v>
